--- a/data/trans_bre/IP16A09-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A09-Estudios-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,81</t>
+          <t>0,0; 11,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 0,0</t>
+          <t>-12,65; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 8,27</t>
+          <t>-0,2; 8,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 1,33</t>
+          <t>-5,84; 1,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 3,03</t>
+          <t>-3,26; 2,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,94; —</t>
+          <t>-47,58; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,93; 101,57</t>
+          <t>-89,75; 80,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 4,48</t>
+          <t>-11,31; 4,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,15</t>
+          <t>0,0; 10,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 0,0</t>
+          <t>-9,48; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 5,65</t>
+          <t>-1,35; 5,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,55</t>
+          <t>-4,01; 1,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,67</t>
+          <t>-2,77; 1,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,93; 565,49</t>
+          <t>-43,07; 478,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-83,39; 138,99</t>
+          <t>-87,85; 117,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-88,19; 351,06</t>
+          <t>-87,21; 352,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A09-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A09-Estudios-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,12</t>
+          <t>0,0; 13,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 0,0</t>
+          <t>-14,86; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 8,31</t>
+          <t>-0,07; 8,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 1,43</t>
+          <t>-5,89; 1,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 2,85</t>
+          <t>-3,58; 3,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-47,58; —</t>
+          <t>-48,06; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-89,75; 80,87</t>
+          <t>-91,33; 111,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 4,53</t>
+          <t>-11,09; 4,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,79</t>
+          <t>0,0; 11,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 0,0</t>
+          <t>-10,28; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 5,3</t>
+          <t>-1,39; 5,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,39</t>
+          <t>-3,71; 1,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,63</t>
+          <t>-3,06; 1,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,07; 478,31</t>
+          <t>-49,95; 532,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-87,85; 117,43</t>
+          <t>-86,19; 118,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-87,21; 352,95</t>
+          <t>-89,78; 418,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A09-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A09-Estudios-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos</t>
+          <t>Menores que consumieron medicamentos para los vómitos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,38</t>
+          <t>0,0; 13,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 0,0</t>
+          <t>-13,27; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,27 +714,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 8,74</t>
+          <t>-0,09; 8,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 1,49</t>
+          <t>-5,8; 1,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 3,08</t>
+          <t>-3,34; 3,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-48,06; —</t>
+          <t>-42,94; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-91,33; 111,4</t>
+          <t>-88,93; 101,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 4,81</t>
+          <t>-11,25; 4,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,37</t>
+          <t>0,0; 11,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 0,0</t>
+          <t>-9,35; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 5,68</t>
+          <t>-1,12; 5,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,37</t>
+          <t>-3,57; 1,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,51</t>
+          <t>-2,69; 1,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-49,95; 532,07</t>
+          <t>-40,93; 565,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,19; 118,52</t>
+          <t>-83,39; 138,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-89,78; 418,88</t>
+          <t>-88,19; 351,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A09-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A09-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,141 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,71</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-2,66</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.6575641967672962</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.7092397263353969</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,81</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-13,27; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.61159195198908</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.672489814352573</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3,59</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,82</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>243,93%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-45,14%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,09; 8,27</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,8; 1,33</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,34; 3,03</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-42,94; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-88,93; 101,57</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.7108531552148465</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.4406969700508606</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.05255110037290459</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>2.629626370128799</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.4379572159172981</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1223570435271718</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,33</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,06</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,86</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-59,23%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.018869735168795</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.617649260887952</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.6272267405356424</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.6033440844915184</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.9154578024481322</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-11,25; 4,48</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,15</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-9,35; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.670483125076412</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.3053946073052342</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.6889833599273671</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="n">
+        <v>1.003180709782613</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,77 +745,151 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,86</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>81,49%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-35,78%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-25,87%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.9568621612008131</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.5656308774022136</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.3731774707709912</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0.7631413855802577</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,12; 5,65</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,57; 1,55</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,69; 1,67</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-40,93; 565,49</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-83,39; 138,99</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-88,19; 351,06</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.160590823922411</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.815991139360452</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1518622437306163</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.368930242851174</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.3098867484483411</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.2510911754118065</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.05253578108600039</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.6837222576656596</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.3376852216569637</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1398155768639447</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.3143908102001732</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.8785266714694648</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.5858416377280756</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.4981586418580389</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.8429438756833357</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9315353940833351</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.380814398045899</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.3923913423397534</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>5.307940206245886</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.370661149899581</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>3.381147932873942</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -913,12 +898,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
